--- a/thailand/FINAL_PANEL.xlsx
+++ b/thailand/FINAL_PANEL.xlsx
@@ -11190,11 +11190,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting Realignment for Balance and Development of Administrative System of the Public Sector</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11268,11 +11264,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Fundamental Program on Realignment for Balance and Development of Administrative System of the Public Sector; Strategic Program on Improvement of Public Service Delivery and the Public Sector's Efficiency; Strategic Program on Supporting Realignment for Balance and Development of Administrative System of the Public Sector</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11346,11 +11338,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting Realignment for Balance and Development of Administrative System of the Public Sector</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11424,11 +11412,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Fundamental Program on Realignment for Balance and Development of Administrative System of the Public Sector; Strategic Program on Improvement of Public Service Delivery and the Public Sector's Efficiency; Strategic Program on Supporting Realignment for Balance and Development of Administrative System of the Public Sector</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11502,11 +11486,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creating Social Security</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11580,11 +11560,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creating Social Security</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11658,11 +11634,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creating Social Security</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11736,11 +11708,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creating Social Security</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11814,11 +11782,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Transport and Logistics System</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11892,11 +11856,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Transport and Logistics System; Strategic Program on Development of Transport and Logistics System</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11970,11 +11930,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Transport and Logistics System</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12048,11 +12004,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Transport and Logistics System</t>
-        </is>
-      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12126,11 +12078,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Integrated Program on Management of Water Resources</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12204,11 +12152,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Integrated Program on Management of Water Resources; Strategic Program on Management of Water Resources</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12282,11 +12226,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Integrated Program on Management of Water Resources</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12360,11 +12300,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Integrated Program on Management of Water Resources</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12438,11 +12374,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Strategic Program on Good Public Health Promotion</t>
-        </is>
-      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12516,11 +12448,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Strategic Program on Good Public Health Promotion</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12594,11 +12522,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Strategic Program on Good Public Health Promotion</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12672,11 +12596,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Strategic Program on Good Public Health Promotion</t>
-        </is>
-      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12750,11 +12670,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Strategic Program on Value Creation Agriculture</t>
-        </is>
-      </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12828,11 +12744,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Strategic Program on Value Creation Agriculture</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12906,11 +12818,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Strategic Program on Value Creation Agriculture</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12984,11 +12892,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Strategic Program on Value Creation Agriculture</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13062,11 +12966,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Human Potentials on a Life-Long Basis</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13140,11 +13040,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Human Potentials on a Life-Long Basis</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13218,11 +13114,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Human Potentials on a Life-Long Basis</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13296,11 +13188,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Human Potentials on a Life-Long Basis</t>
-        </is>
-      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13374,11 +13262,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Strategic Program on Improvement of Public Service Delivery and the Public Sector's Efficiency</t>
-        </is>
-      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13452,11 +13336,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Strategic Program on Improvement of Public Service Delivery and the Public Sector's Efficiency</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13530,11 +13410,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Strategic Program on Improvement of Public Service Delivery and the Public Sector's Efficiency</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13608,11 +13484,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Strategic Program on Improvement of Public Service Delivery and the Public Sector's Efficiency</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13686,11 +13558,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Education and Learning Quality</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13764,11 +13632,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Education and Learning Quality</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -13842,11 +13706,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Education and Learning Quality</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -13920,11 +13780,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Education and Learning Quality</t>
-        </is>
-      </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13998,11 +13854,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting Development of Competitiveness</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14076,11 +13928,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting the Development of Competitiveness</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14154,11 +14002,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting the Development of Competitiveness</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14232,11 +14076,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting the Development of Competitiveness</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14310,11 +14150,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing National Preparedness System and Disaster Management System</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14388,11 +14224,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing National Preparedness System and Disaster Management System</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14466,11 +14298,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing National Preparedness System and Disaster Management System</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14544,11 +14372,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing National Preparedness System and Disaster Management System</t>
-        </is>
-      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14622,11 +14446,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services; Strategic Program on Innovation Research and Development</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14700,11 +14520,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services; Strategic Program on Innovation Research and Development</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14778,11 +14594,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services; Strategic Program on Research and Innovation Development</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14856,11 +14668,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Strategic Program on Research and Innovation Development</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14934,11 +14742,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creation of Sustainable Growth with Regard to Conservation, Rehabilitation and Prevention of Natural Resources Destruction; Strategic Program on Dealing with Pollution and the Environment; Strategic Program on Supporting Creation of Growth on the Environmental-friendly Quality of Life</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15012,11 +14816,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Fundamental Program on Creation of Growth on the Environmental-friendly Quality of Life; Strategic Program on Dealing with Pollution and the Environment; Strategic Program on Elevating Paradigms to Stipulate the Future of the Country's Natural Resources and Environment; Strategic Program on Supporting Creation of Growth on the Environmental-friendly Quality of Life</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15090,11 +14890,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Fundamental Program on Creation of Growth on the Environmental-friendly Quality of Life; Strategic Program on Dealing with Pollution and the Environment; Strategic Program on Supporting Creation of Growth on the Environmental-friendly Quality of Life</t>
-        </is>
-      </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15168,11 +14964,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Strategic Program on Dealing with Pollution and the Environment; Strategic Program on Supporting Creation of Growth on the Environmental-friendly Quality of Life</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15246,11 +15038,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing Laws and the Judicial Process</t>
-        </is>
-      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15324,11 +15112,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing Laws and the Judicial Process</t>
-        </is>
-      </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15402,11 +15186,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing Laws and the Judicial Process</t>
-        </is>
-      </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15480,11 +15260,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Strategic Program on Developing Laws and the Judicial Process</t>
-        </is>
-      </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15558,11 +15334,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Strategic Program on Area Development and Smart Livable City</t>
-        </is>
-      </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15636,11 +15408,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Strategic Program on Area Development and Smart Livable City</t>
-        </is>
-      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15714,11 +15482,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Strategic Program on Area Development and Smart Livable City</t>
-        </is>
-      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15792,11 +15556,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Strategic Program on Area Development and Smart Livable City</t>
-        </is>
-      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15870,11 +15630,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of the Eastern Economic Corridor</t>
-        </is>
-      </c>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -15948,11 +15704,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of the Eastern Economic Corridor</t>
-        </is>
-      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16026,11 +15778,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of the Eastern Economic Corridor</t>
-        </is>
-      </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -16104,11 +15852,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of the Eastern Economic Corridor</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16182,11 +15926,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Strategic Program on Social Empowerment</t>
-        </is>
-      </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16260,11 +16000,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Strategic Program on Social Empowerment</t>
-        </is>
-      </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -16338,11 +16074,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Strategic Program on Social Empowerment</t>
-        </is>
-      </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -16416,11 +16148,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Strategic Program on Social Empowerment</t>
-        </is>
-      </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -16494,11 +16222,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Integrated Program on Creating Income from Tourism</t>
-        </is>
-      </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -16572,11 +16296,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Integrated Program on Creating Income from Tourism</t>
-        </is>
-      </c>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -16650,11 +16370,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Integrated Program on Creating Income from Tourism</t>
-        </is>
-      </c>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16728,11 +16444,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Integrated Program on Creating Income from Tourism</t>
-        </is>
-      </c>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -16806,11 +16518,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creation of Sustainable Growth with Regard to Conservation, Rehabilitation and Prevention of Natural Resources Destruction; Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -16884,11 +16592,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creation of Sustainable Growth with Regard to Conservation, Rehabilitation and Prevention of Natural Resources Destruction</t>
-        </is>
-      </c>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -16962,11 +16666,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creation of Sustainable Growth with Regard to Conservation, Rehabilitation and Prevention of Natural Resources Destruction; Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17040,11 +16740,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Strategic Program on Creation of Sustainable Growth with Regard to Conservation, Rehabilitation and Prevention of Natural Resources Destruction; Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17118,11 +16814,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Strategic Program on Promoting International Relations</t>
-        </is>
-      </c>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17196,11 +16888,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Strategic Program on Promoting International Relations</t>
-        </is>
-      </c>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -17274,11 +16962,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Strategic Program on Promoting International Relations</t>
-        </is>
-      </c>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17352,11 +17036,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Strategic Program on Promoting International Relations</t>
-        </is>
-      </c>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -17430,11 +17110,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting Strong and Competitive Small and Medium-sized Enterprises</t>
-        </is>
-      </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -17508,11 +17184,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting Strong and Competitive Small and Medium-sized Enterprises</t>
-        </is>
-      </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -17586,11 +17258,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting Strong and Competitive Small and Medium-sized Enterprises</t>
-        </is>
-      </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -17664,11 +17332,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Strategic Program on Supporting Strong and Competitive Small and Medium-sized Enterprises</t>
-        </is>
-      </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -17742,11 +17406,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services</t>
-        </is>
-      </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -17820,11 +17480,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services</t>
-        </is>
-      </c>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -17898,11 +17554,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services</t>
-        </is>
-      </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -17976,11 +17628,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services</t>
-        </is>
-      </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18054,11 +17702,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Integrated Program on Digital Government</t>
-        </is>
-      </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18132,11 +17776,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Integrated Program on Digital Government</t>
-        </is>
-      </c>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -18210,11 +17850,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Integrated Program on Digital Government</t>
-        </is>
-      </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18288,11 +17924,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Integrated Program on Digital Government</t>
-        </is>
-      </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18366,11 +17998,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services; Strategic Program on Development of Science, Technology and Innovation Potentials</t>
-        </is>
-      </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18444,11 +18072,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services; Strategic Program on Development of Science, Technology and Innovation Potentials</t>
-        </is>
-      </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18522,11 +18146,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Integrated Program on Development of Future Industries and Services; Strategic Program on Development of Science, Technology and Innovation Potentials</t>
-        </is>
-      </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18674,11 +18294,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Strategic Program on Coping with Repercussions from Climate Change; Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18752,11 +18368,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Strategic Program on Coping with Repercussions from Climate Change</t>
-        </is>
-      </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -18830,11 +18442,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Strategic Program on Coping with Repercussions from Climate Change; Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -18908,11 +18516,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Strategic Program on Coping with Repercussions from Climate Change; Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -18986,11 +18590,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Digital Economy and Society</t>
-        </is>
-      </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19064,11 +18664,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Digital Economy and Society</t>
-        </is>
-      </c>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19142,11 +18738,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Digital Economy and Society</t>
-        </is>
-      </c>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19220,11 +18812,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Digital Economy and Society</t>
-        </is>
-      </c>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19298,11 +18886,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Energy Security</t>
-        </is>
-      </c>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19376,11 +18960,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Energy Security</t>
-        </is>
-      </c>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19454,11 +19034,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Energy Security</t>
-        </is>
-      </c>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -19532,11 +19108,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Energy Security</t>
-        </is>
-      </c>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -19610,11 +19182,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -19688,11 +19256,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -19766,11 +19330,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -19844,11 +19404,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Strategic Program on Dealing with Pollution and the Environment</t>
-        </is>
-      </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -19922,11 +19478,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Integrated Program on Preparedness to Accommodate the Aging Society</t>
-        </is>
-      </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20000,11 +19552,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Integrated Program on Preparedness to Accommodate the Aging Society</t>
-        </is>
-      </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -20078,11 +19626,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Integrated Program on Preparedness to Accommodate the Aging Society</t>
-        </is>
-      </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20156,11 +19700,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>Integrated Program on Preparedness to Accommodate the Aging Society</t>
-        </is>
-      </c>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20234,11 +19774,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Special Economic Zones</t>
-        </is>
-      </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20312,11 +19848,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Special Economic Zones</t>
-        </is>
-      </c>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20390,11 +19922,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Special Economic Zones</t>
-        </is>
-      </c>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20468,11 +19996,7 @@
           <t>million baht</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Strategic Program on Development of Special Economic Zones</t>
-        </is>
-      </c>
+      <c r="P121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
